--- a/output/pdf_financials_xlsx/ILLM.xlsx
+++ b/output/pdf_financials_xlsx/ILLM.xlsx
@@ -1669,7 +1669,7 @@
         <v>0.234305</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.423788</v>
+        <v>10.342707</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.246832</v>
@@ -1714,7 +1714,7 @@
         <v>-6.333988</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.386539</v>
+        <v>6.53238</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0.467437</v>
@@ -1759,7 +1759,7 @@
         <v>-46.39520852466327</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-16.36510093137687</v>
+        <v>31.56705356770072</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1.180345077906204</v>
@@ -14052,7 +14052,11 @@
           <t>Additions to intangible assets (note 4)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17788,7 +17792,11 @@
           <t>Additions to intangible assets (note 7)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -20182,7 +20190,11 @@
           <t>Additions to intangible assets (note 6)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -40470,7 +40482,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -40546,7 +40562,11 @@
           <t>Depreciation of property and equipment total</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
